--- a/modeleLogiqueSBM/ig/FRObservationTransfusionAccidentsLMCDAFHIR.xlsx
+++ b/modeleLogiqueSBM/ig/FRObservationTransfusionAccidentsLMCDAFHIR.xlsx
@@ -55,7 +55,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-07T14:19:51+00:00</t>
+    <t>2026-04-07T14:45:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/modeleLogiqueSBM/ig/FRObservationTransfusionAccidentsLMCDAFHIR.xlsx
+++ b/modeleLogiqueSBM/ig/FRObservationTransfusionAccidentsLMCDAFHIR.xlsx
@@ -55,7 +55,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-07T14:45:49+00:00</t>
+    <t>2026-04-08T10:07:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/modeleLogiqueSBM/ig/FRObservationTransfusionAccidentsLMCDAFHIR.xlsx
+++ b/modeleLogiqueSBM/ig/FRObservationTransfusionAccidentsLMCDAFHIR.xlsx
@@ -55,7 +55,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-08T10:07:24+00:00</t>
+    <t>2026-04-08T12:33:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
